--- a/data/tennis_court/data.xlsx
+++ b/data/tennis_court/data.xlsx
@@ -682,7 +682,7 @@
         <v>高松市庵治町6391-17</v>
       </c>
       <c r="F8" t="str">
-        <v>087-845-7060</v>
+        <v>087-845-1563</v>
       </c>
       <c r="G8" t="str">
         <v>http://www.taka-spo.or.jp/fuk1.html</v>
